--- a/data/raw/sales/Week 25/Audio_Array/Vendor Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 25/Audio_Array/Vendor Sales (SP-API).xlsx
@@ -543,7 +543,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
